--- a/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 23,72</t>
+          <t>-9,95; 22,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 22,79</t>
+          <t>-11,88; 23,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 27,53</t>
+          <t>-14,21; 24,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 17,46</t>
+          <t>-11,48; 15,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 29,31</t>
+          <t>-10,45; 24,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 27,33</t>
+          <t>-7,77; 28,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 15,73</t>
+          <t>-6,58; 15,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 17,38</t>
+          <t>-7,38; 17,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 18,88</t>
+          <t>-7,72; 18,39</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,15; —</t>
+          <t>-65,56; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 813,06</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 498,43</t>
+          <t>-59,55; 418,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 610,48</t>
+          <t>-77,56; 511,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 584,46</t>
+          <t>-72,55; 506,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 17,88</t>
+          <t>0,02; 17,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 8,04</t>
+          <t>-6,21; 8,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 7,8</t>
+          <t>-9,4; 7,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 11,31</t>
+          <t>-4,19; 10,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 10,67</t>
+          <t>-4,63; 11,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -1,36</t>
+          <t>-12,89; -1,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 11,91</t>
+          <t>-0,43; 11,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 7,21</t>
+          <t>-3,56; 7,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,7</t>
+          <t>-8,58; 0,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 262,8</t>
+          <t>-2,51; 298,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 127,78</t>
+          <t>-47,87; 132,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 126,32</t>
+          <t>-72,5; 132,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 183,57</t>
+          <t>-34,62; 164,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 192,59</t>
+          <t>-38,35; 183,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,85; -3,13</t>
+          <t>-87,56; -4,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 156,34</t>
+          <t>-6,32; 147,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 101,81</t>
+          <t>-29,15; 111,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,68; 10,92</t>
+          <t>-70,11; 16,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 23,9</t>
+          <t>-0,67; 23,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 22,36</t>
+          <t>-3,43; 24,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 12,63</t>
+          <t>-7,52; 12,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 14,6</t>
+          <t>-10,83; 15,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 16,57</t>
+          <t>-12,5; 17,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 7,9</t>
+          <t>-16,95; 6,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 15,41</t>
+          <t>-4,27; 14,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 15,1</t>
+          <t>-4,28; 14,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 6,28</t>
+          <t>-9,6; 5,9</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,67; —</t>
+          <t>-44,24; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,1; —</t>
+          <t>-69,2; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,79; —</t>
+          <t>-76,38; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 256,99</t>
+          <t>-63,44; 222,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 270,06</t>
+          <t>-69,6; 224,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,85; 156,14</t>
+          <t>-88,94; 112,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,99; 255,48</t>
+          <t>-29,88; 286,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 243,34</t>
+          <t>-34,96; 252,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 120,7</t>
+          <t>-65,63; 116,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 16,15</t>
+          <t>2,5; 15,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,48</t>
+          <t>-3,03; 8,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,73</t>
+          <t>-6,73; 5,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 8,47</t>
+          <t>-3,4; 8,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 8,8</t>
+          <t>-3,71; 9,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -0,39</t>
+          <t>-9,6; 0,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,42</t>
+          <t>1,35; 10,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 7,28</t>
+          <t>-1,52; 7,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,59</t>
+          <t>-6,46; 1,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,17; 285,28</t>
+          <t>17,39; 254,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 135,96</t>
+          <t>-30,02; 137,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 105,53</t>
+          <t>-56,81; 95,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 117,3</t>
+          <t>-27,63; 118,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 120,47</t>
+          <t>-29,38; 131,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 1,78</t>
+          <t>-73,18; 6,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 130,02</t>
+          <t>9,3; 131,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 98,72</t>
+          <t>-13,33; 98,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 22,61</t>
+          <t>-55,43; 20,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 22,93</t>
+          <t>-8,74; 22,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 23,26</t>
+          <t>-11,94; 23,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 24,81</t>
+          <t>-13,9; 24,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 15,78</t>
+          <t>-10,28; 15,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 24,73</t>
+          <t>-9,87; 27,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 28,21</t>
+          <t>-10,26; 24,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 15,47</t>
+          <t>-5,13; 15,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 17,02</t>
+          <t>-8,07; 17,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 18,39</t>
+          <t>-7,46; 18,04</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,56; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 813,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 418,39</t>
+          <t>-57,25; 540,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 511,33</t>
+          <t>-82,24; 495,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 506,22</t>
+          <t>-78,71; 476,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 17,9</t>
+          <t>0,81; 17,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 8,35</t>
+          <t>-6,38; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 7,52</t>
+          <t>-9,88; 7,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 10,81</t>
+          <t>-4,3; 10,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 11,82</t>
+          <t>-3,96; 10,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,51</t>
+          <t>-12,9; -1,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 11,35</t>
+          <t>-0,25; 11,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 7,72</t>
+          <t>-3,53; 7,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,92</t>
+          <t>-8,98; 0,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 298,4</t>
+          <t>1,62; 282,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 132,33</t>
+          <t>-48,49; 143,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 132,78</t>
+          <t>-73,22; 125,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 164,79</t>
+          <t>-33,63; 173,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 183,82</t>
+          <t>-31,62; 180,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,56; -4,18</t>
+          <t>-88,02; -9,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 147,81</t>
+          <t>-2,74; 161,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 111,23</t>
+          <t>-30,52; 106,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 16,7</t>
+          <t>-71,12; 21,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 23,21</t>
+          <t>-1,24; 23,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 24,0</t>
+          <t>-4,38; 21,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 12,32</t>
+          <t>-7,87; 12,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 15,61</t>
+          <t>-12,17; 12,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 17,23</t>
+          <t>-10,8; 17,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 6,49</t>
+          <t>-16,96; 6,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 14,79</t>
+          <t>-4,45; 14,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 14,89</t>
+          <t>-4,39; 16,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 5,9</t>
+          <t>-10,55; 6,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,24; —</t>
+          <t>-51,2; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,2; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,38; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 222,44</t>
+          <t>-64,64; 210,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,6; 224,01</t>
+          <t>-67,97; 309,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,94; 112,16</t>
+          <t>-88,02; 118,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 286,06</t>
+          <t>-33,95; 284,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 252,3</t>
+          <t>-33,33; 308,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,63; 116,58</t>
+          <t>-70,86; 131,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,44</t>
+          <t>2,68; 15,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,47</t>
+          <t>-3,51; 8,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,75</t>
+          <t>-6,47; 5,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 8,47</t>
+          <t>-2,75; 9,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,79</t>
+          <t>-3,2; 9,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 0,18</t>
+          <t>-9,98; 0,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,31</t>
+          <t>1,43; 10,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 7,64</t>
+          <t>-1,59; 7,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 1,51</t>
+          <t>-6,72; 1,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,39; 254,07</t>
+          <t>19,25; 250,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 137,43</t>
+          <t>-31,27; 129,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 95,67</t>
+          <t>-59,12; 90,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 118,86</t>
+          <t>-22,72; 130,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 131,54</t>
+          <t>-27,38; 123,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,18; 6,44</t>
+          <t>-75,17; 3,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,3; 131,54</t>
+          <t>10,89; 141,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 98,53</t>
+          <t>-13,63; 100,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 20,74</t>
+          <t>-56,96; 16,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>6,55</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 22,43</t>
+          <t>-9,94; 17,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 23,66</t>
+          <t>-10,17; 29,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 24,91</t>
+          <t>-7,31; 31,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 15,81</t>
+          <t>-7,8; 23,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 27,98</t>
+          <t>-10,95; 22,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 24,77</t>
+          <t>-9,99; 29,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 15,96</t>
+          <t>-6,04; 15,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 17,02</t>
+          <t>-8,01; 17,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 18,04</t>
+          <t>-4,55; 23,3</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>107,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>81,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>36,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-60,15; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 540,01</t>
+          <t>-54,95; 498,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,24; 495,51</t>
+          <t>-74,71; 610,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 476,64</t>
+          <t>-59,26; 889,04</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,81</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-6,88</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,66</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-4,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 17,49</t>
+          <t>-4,52; 11,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 8,22</t>
+          <t>-4,98; 10,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 7,87</t>
+          <t>-13,32; -1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,8</t>
+          <t>0,05; 17,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 10,73</t>
+          <t>-7,69; 8,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,9; -1,12</t>
+          <t>-8,66; 4,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 11,96</t>
+          <t>0,04; 11,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 7,5</t>
+          <t>-3,35; 7,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 0,72</t>
+          <t>-9,47; -0,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-68,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>92,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,13%</t>
+          <t>-22,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-42,83%</t>
+          <t>-47,5%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 282,45</t>
+          <t>-34,46; 183,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,49; 143,27</t>
+          <t>-37,14; 192,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,22; 125,97</t>
+          <t>-87,8; -7,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 173,44</t>
+          <t>-10,34; 262,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 180,58</t>
+          <t>-52,73; 127,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,02; -9,52</t>
+          <t>-64,33; 92,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 161,99</t>
+          <t>-0,36; 156,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 106,71</t>
+          <t>-27,93; 101,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 21,47</t>
+          <t>-72,63; -4,02</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,22</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,8</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 23,94</t>
+          <t>-11,6; 14,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 21,76</t>
+          <t>-11,02; 16,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 12,24</t>
+          <t>-16,38; 8,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 12,86</t>
+          <t>-1,11; 23,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 17,4</t>
+          <t>-3,58; 22,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 6,72</t>
+          <t>-9,65; 11,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 14,75</t>
+          <t>-3,93; 15,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 16,12</t>
+          <t>-5,47; 15,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 6,05</t>
+          <t>-9,87; 6,06</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-34,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>189,43%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>152,58%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>51,43%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-34,9%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,42%</t>
+          <t>-17,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,2; —</t>
+          <t>-63,46; 256,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,46; 270,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,06; 162,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 210,22</t>
+          <t>-31,67; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 309,55</t>
+          <t>-72,1; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 118,05</t>
+          <t>-83,33; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 284,61</t>
+          <t>-36,99; 255,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 308,98</t>
+          <t>-42,92; 243,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,86; 131,23</t>
+          <t>-65,67; 117,47</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,84</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,47</t>
+          <t>-3,72; 8,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,14</t>
+          <t>-3,5; 8,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,85</t>
+          <t>-10,3; -0,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,44</t>
+          <t>2,11; 16,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 9,4</t>
+          <t>-3,3; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,04</t>
+          <t>-5,9; 4,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,54</t>
+          <t>0,94; 10,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 7,57</t>
+          <t>-1,53; 7,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,18</t>
+          <t>-6,73; 0,74</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,35%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-47,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>100,58%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-5,1%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,55%</t>
+          <t>-6,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-28,36%</t>
+          <t>-29,65%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,25; 250,74</t>
+          <t>-27,73; 117,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 129,42</t>
+          <t>-30,75; 120,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 90,58</t>
+          <t>-76,59; 5,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 130,75</t>
+          <t>16,17; 285,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 123,12</t>
+          <t>-30,36; 135,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 3,94</t>
+          <t>-50,1; 81,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,89; 141,59</t>
+          <t>5,61; 130,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 100,71</t>
+          <t>-13,67; 98,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 16,9</t>
+          <t>-56,71; 13,24</t>
         </is>
       </c>
     </row>
